--- a/sheets/민요/검수/영천 아리랑.xlsx
+++ b/sheets/민요/검수/영천 아리랑.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4085,8 +4192,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4105,1042 +4216,1057 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">영천 아리랑 — 민요채보-2/영천 아리랑.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">영천 아리랑</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">애</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">열</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 潢</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="I4" s="14"/>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K4" s="14"/>
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O4" s="14"/>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">린</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="E6" s="13"/>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M6" s="13"/>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O6" s="13"/>
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="Q6" s="13"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="14"/>
+      <c r="L7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">재</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="15"/>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="15"/>
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="15"/>
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="I8" s="15"/>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K8" s="15"/>
+      <c r="L8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="15"/>
+      <c r="N8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q8" s="15"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E9" s="13"/>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">넘</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O9" s="13"/>
+      <c r="P9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">겨</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">났</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="Q10" s="14"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">골</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K11" s="15"/>
+      <c r="L11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="M11" s="15"/>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O11" s="15"/>
+      <c r="P11" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q11" s="15"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">집</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="13"/>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">쓸</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="14"/>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="14"/>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G13" s="14"/>
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" s="14"/>
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林</t>
         </is>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="14"/>
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="O13" s="14"/>
+      <c r="P13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="Q13" s="14"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="15"/>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="E14" s="15"/>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="15"/>
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="M14" s="15"/>
+      <c r="N14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 潢</t>
         </is>
       </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="O14" s="15"/>
+      <c r="P14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 潢</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/영천 아리랑.xlsx
+++ b/sheets/민요/검수/영천 아리랑.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -597,13 +597,13 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―林</t>
+          <t xml:space="preserve">姑|–林</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―林</t>
+–林</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -848,13 +848,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">林|―潢</t>
+          <t xml:space="preserve">林|–潢</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -933,14 +933,14 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰|―</t>
+          <t xml:space="preserve">潢|汰|–</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I11" s="2"/>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|林</t>
+          <t xml:space="preserve">–|林</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 林</t>
         </is>
       </c>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -1401,13 +1401,13 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―潢</t>
+          <t xml:space="preserve">仲|–潢</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I23" s="2"/>
@@ -1775,13 +1775,13 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―潢</t>
+          <t xml:space="preserve">仲|–潢</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -1856,13 +1856,13 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―潢</t>
+          <t xml:space="preserve">仲|–潢</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I35" s="2"/>
@@ -1892,13 +1892,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―潢</t>
+          <t xml:space="preserve">汰|–潢</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -2166,13 +2166,13 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―潢</t>
+          <t xml:space="preserve">仲|–潢</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -2286,13 +2286,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―潢</t>
+          <t xml:space="preserve">仲|–潢</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I46" s="2"/>
@@ -2757,13 +2757,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―潢</t>
+          <t xml:space="preserve">仲|–潢</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I58" s="2"/>
@@ -2793,13 +2793,13 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―汰</t>
+          <t xml:space="preserve">仲|–汰</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -2829,13 +2829,13 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―汰</t>
+          <t xml:space="preserve">汰|–汰</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="I60" s="2"/>
@@ -3065,12 +3065,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="I66" s="2"/>
@@ -3100,13 +3100,13 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―潢</t>
+          <t xml:space="preserve">仲|–潢</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3492,13 +3492,13 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―潢</t>
+          <t xml:space="preserve">仲|–潢</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4032,13 +4032,13 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―潢</t>
+          <t xml:space="preserve">仲|–潢</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       <c r="P4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―林</t>
+–林</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
@@ -4603,7 +4603,7 @@
       <c r="D6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -4649,7 +4649,7 @@
       <c r="M6" s="8"/>
       <c r="N6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 林</t>
         </is>
       </c>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="G7" s="9"/>
@@ -4746,7 +4746,7 @@
       <c r="B8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -4763,7 +4763,7 @@
       <c r="F8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -4780,7 +4780,7 @@
       <c r="J8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
@@ -4943,7 +4943,7 @@
       <c r="L10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="M10" s="12" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -4961,7 +4961,7 @@
       <c r="P10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr">
@@ -5001,14 +5001,14 @@
       <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="K11" s="10"/>
@@ -5067,7 +5067,7 @@
       <c r="H12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="I12" s="8"/>
@@ -5080,14 +5080,14 @@
       <c r="L12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="M12" s="8"/>
       <c r="N12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="O12" s="8"/>
@@ -5095,7 +5095,7 @@
         <is>
           <t xml:space="preserve">潢
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="Q12" s="8"/>
@@ -5123,7 +5123,7 @@
       <c r="H13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="I13" s="9"/>
@@ -5136,7 +5136,7 @@
       <c r="L13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="M13" s="9"/>

--- a/sheets/민요/검수/영천 아리랑.xlsx
+++ b/sheets/민요/검수/영천 아리랑.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4291,117 +4332,117 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">영천 아리랑</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 潢</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">열</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林
 姑</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 潢</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 潢</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">애</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">열</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P3" s="18" t="inlineStr">
+      <c r="P3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 姑</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4409,7 +4450,7 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林
@@ -4417,85 +4458,85 @@
 △</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林
 姑</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">론</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林
 姑</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">르</t>
         </is>
       </c>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林
 姑</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –林</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -4503,86 +4544,86 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑
 △</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="Q5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">린</t>
         </is>
@@ -4590,78 +4631,78 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">애</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 林</t>
         </is>
       </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="18" t="inlineStr">
+      <c r="O6" s="22"/>
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑
 ‹</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -4669,73 +4710,73 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="G7" s="26"/>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I7" s="26"/>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M7" s="26"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑
 △</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="Q7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4743,69 +4784,69 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E8" s="27"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="I8" s="28"/>
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="K8" s="13" t="inlineStr">
+      <c r="K8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="18" t="inlineStr">
+      <c r="M8" s="28"/>
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P8" s="18" t="inlineStr">
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑
@@ -4813,7 +4854,7 @@
 △</t>
         </is>
       </c>
-      <c r="Q8" s="13" t="inlineStr">
+      <c r="Q8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">영</t>
         </is>
@@ -4821,78 +4862,78 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E9" s="22"/>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">넘</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑
 仲</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">린</t>
         </is>
@@ -4900,71 +4941,71 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C10" s="26"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E10" s="26"/>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 仲</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K10" s="26"/>
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">넘</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="18" t="inlineStr">
+      <c r="O10" s="26"/>
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 –潢</t>
         </is>
       </c>
-      <c r="Q10" s="12" t="inlineStr">
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4972,73 +5013,73 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="27"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="27"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑
 仲</t>
         </is>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="M11" s="27"/>
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O11" s="13" t="inlineStr">
+      <c r="O11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢
 仲</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="Q11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -5046,168 +5087,168 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –汰</t>
         </is>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="M12" s="22"/>
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="O12" s="22"/>
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 –</t>
         </is>
       </c>
-      <c r="Q12" s="8"/>
+      <c r="Q12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C13" s="26"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E13" s="26"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –汰</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="I13" s="26"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K13" s="26"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –潢</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="26"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 林
 姑</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="26"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 潢</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
+      <c r="Q13" s="26"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E14" s="27"/>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I14" s="27"/>
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q14" s="10"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M14" s="27"/>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O14" s="27"/>
+      <c r="P14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/영천 아리랑.xlsx
+++ b/sheets/민요/검수/영천 아리랑.xlsx
@@ -4309,28 +4309,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="108.96" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="108.96" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="108.96" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="108.96" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="108.96" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -4708,7 +4708,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="108.96" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
       <c r="G7" s="26"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="26"/>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M7" s="26"/>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="108.96" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E8" s="27"/>
@@ -4860,17 +4860,17 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="108.96" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -4939,17 +4939,17 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="108.96" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="26"/>
@@ -5011,11 +5011,11 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="108.96" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C11" s="27"/>
@@ -5085,23 +5085,23 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="108.96" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -5114,7 +5114,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -5141,23 +5141,23 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="108.96" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="26"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E13" s="26"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G13" s="26"/>
@@ -5170,7 +5170,7 @@
       <c r="I13" s="26"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="26"/>
@@ -5198,35 +5198,35 @@
       </c>
       <c r="Q13" s="26"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="108.96" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="27"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="27"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="27"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -5239,13 +5239,13 @@
       <c r="M14" s="27"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O14" s="27"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q14" s="27"/>

--- a/sheets/민요/검수/영천 아리랑.xlsx
+++ b/sheets/민요/검수/영천 아리랑.xlsx
@@ -718,14 +718,13 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">林|姑|‹</t>
+          <t xml:space="preserve">林|姑</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-姑
-‹</t>
+姑</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4698,8 +4697,7 @@
       <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-姑
-‹</t>
+姑</t>
         </is>
       </c>
       <c r="Q6" s="24" t="inlineStr">

--- a/sheets/민요/검수/영천 아리랑.xlsx
+++ b/sheets/민요/검수/영천 아리랑.xlsx
@@ -2432,13 +2432,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I49" s="3"/>
@@ -5224,8 +5223,7 @@
       <c r="I14" s="27"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="28"/>

--- a/sheets/민요/검수/영천 아리랑.xlsx
+++ b/sheets/민요/검수/영천 아리랑.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4360,7 +4383,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">열</t>
         </is>
@@ -4371,7 +4394,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4383,7 +4406,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -4395,7 +4418,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -4407,7 +4430,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">애</t>
         </is>
@@ -4418,7 +4441,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">열</t>
         </is>
@@ -4429,7 +4452,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4440,7 +4463,7 @@
 姑</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="inlineStr">
+      <c r="Q3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4456,7 +4479,7 @@
 △</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
@@ -4468,7 +4491,7 @@
 姑</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
@@ -4479,7 +4502,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">론</t>
         </is>
@@ -4491,7 +4514,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I4" s="26" t="inlineStr">
+      <c r="I4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">르</t>
         </is>
@@ -4503,7 +4526,7 @@
 姑</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
@@ -4513,7 +4536,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
@@ -4523,7 +4546,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
+      <c r="O4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
@@ -4534,7 +4557,7 @@
 –林</t>
         </is>
       </c>
-      <c r="Q4" s="26" t="inlineStr">
+      <c r="Q4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -4547,7 +4570,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -4558,7 +4581,7 @@
 姑</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4570,7 +4593,7 @@
 △</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -4580,7 +4603,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I5" s="28" t="inlineStr">
+      <c r="I5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -4590,7 +4613,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4600,7 +4623,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -4610,7 +4633,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="O5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4621,7 +4644,7 @@
 林</t>
         </is>
       </c>
-      <c r="Q5" s="27" t="inlineStr">
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">린</t>
         </is>
@@ -4634,7 +4657,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">애</t>
         </is>
@@ -4645,7 +4668,7 @@
 –潢</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
@@ -4655,7 +4678,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
@@ -4665,7 +4688,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
@@ -4675,7 +4698,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4685,21 +4708,21 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M6" s="22"/>
+      <c r="M6" s="29"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 林</t>
         </is>
       </c>
-      <c r="O6" s="22"/>
+      <c r="O6" s="29"/>
       <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="Q6" s="24" t="inlineStr">
+      <c r="Q6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -4712,7 +4735,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
@@ -4722,7 +4745,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
@@ -4732,19 +4755,19 @@
           <t xml:space="preserve">–潢</t>
         </is>
       </c>
-      <c r="G7" s="26"/>
+      <c r="G7" s="32"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I7" s="26"/>
+      <c r="I7" s="32"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K7" s="26" t="inlineStr">
+      <c r="K7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
@@ -4754,7 +4777,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M7" s="26"/>
+      <c r="M7" s="32"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
@@ -4762,7 +4785,7 @@
 △</t>
         </is>
       </c>
-      <c r="O7" s="26" t="inlineStr">
+      <c r="O7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4773,7 +4796,7 @@
 南</t>
         </is>
       </c>
-      <c r="Q7" s="26" t="inlineStr">
+      <c r="Q7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4787,7 +4810,7 @@
 –潢</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4797,14 +4820,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="33"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
@@ -4814,14 +4837,14 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I8" s="28"/>
+      <c r="I8" s="34"/>
       <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="K8" s="28" t="inlineStr">
+      <c r="K8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
@@ -4831,14 +4854,14 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M8" s="28"/>
+      <c r="M8" s="34"/>
       <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O8" s="28" t="inlineStr">
+      <c r="O8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4851,7 +4874,7 @@
 △</t>
         </is>
       </c>
-      <c r="Q8" s="28" t="inlineStr">
+      <c r="Q8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">영</t>
         </is>
@@ -4864,19 +4887,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -4886,7 +4909,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">넘</t>
         </is>
@@ -4898,7 +4921,7 @@
 仲</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
@@ -4908,7 +4931,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -4919,7 +4942,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4930,7 +4953,7 @@
 姑</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">린</t>
         </is>
@@ -4943,20 +4966,20 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C10" s="26"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="26"/>
+      <c r="E10" s="32"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -4967,7 +4990,7 @@
 仲</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
@@ -4977,14 +5000,14 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K10" s="26"/>
+      <c r="K10" s="32"/>
       <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">넘</t>
         </is>
@@ -4995,14 +5018,14 @@
 仲</t>
         </is>
       </c>
-      <c r="O10" s="26"/>
+      <c r="O10" s="32"/>
       <c r="P10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 –潢</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="Q10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5015,13 +5038,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -5031,7 +5054,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G11" s="27" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -5042,14 +5065,14 @@
 –潢</t>
         </is>
       </c>
-      <c r="I11" s="27"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="K11" s="27"/>
+      <c r="K11" s="33"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
@@ -5057,14 +5080,14 @@
 仲</t>
         </is>
       </c>
-      <c r="M11" s="27"/>
+      <c r="M11" s="33"/>
       <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O11" s="28" t="inlineStr">
+      <c r="O11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5076,7 +5099,7 @@
 仲</t>
         </is>
       </c>
-      <c r="Q11" s="27" t="inlineStr">
+      <c r="Q11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -5089,46 +5112,46 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="29"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –汰</t>
         </is>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="29"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K12" s="22"/>
+      <c r="K12" s="29"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="M12" s="22"/>
+      <c r="M12" s="29"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –潢</t>
         </is>
       </c>
-      <c r="O12" s="22"/>
+      <c r="O12" s="29"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
@@ -5136,7 +5159,7 @@
 –</t>
         </is>
       </c>
-      <c r="Q12" s="22"/>
+      <c r="Q12" s="29"/>
     </row>
     <row r="13" ht="108.96" customHeight="1">
       <c r="A13" s="0"/>
@@ -5145,39 +5168,39 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="26"/>
+      <c r="C13" s="32"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="26"/>
+      <c r="E13" s="32"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="32"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –汰</t>
         </is>
       </c>
-      <c r="I13" s="26"/>
+      <c r="I13" s="32"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="26"/>
+      <c r="K13" s="32"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –潢</t>
         </is>
       </c>
-      <c r="M13" s="26"/>
+      <c r="M13" s="32"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
@@ -5185,7 +5208,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O13" s="26"/>
+      <c r="O13" s="32"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
@@ -5193,7 +5216,7 @@
 潢</t>
         </is>
       </c>
-      <c r="Q13" s="26"/>
+      <c r="Q13" s="32"/>
     </row>
     <row r="14" ht="108.96" customHeight="1">
       <c r="A14" s="0"/>
@@ -5202,49 +5225,49 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="27"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="28"/>
+      <c r="K14" s="34"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="33"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O14" s="27"/>
+      <c r="O14" s="33"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="27"/>
+      <c r="Q14" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/영천 아리랑.xlsx
+++ b/sheets/민요/검수/영천 아리랑.xlsx
@@ -643,10 +643,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/영천 아리랑.xlsx
+++ b/sheets/민요/검수/영천 아리랑.xlsx
@@ -589,17 +589,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -716,7 +716,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -774,6 +774,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2716,324 +2760,324 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:M10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="52.63" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="19" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="22" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="20"/>
+      <c r="F5" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="20"/>
+      <c r="H5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="20" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B6" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="23"/>
+      <c r="F6" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="23" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="M7" s="24" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="7" t="s">
+      <c r="G8" s="20"/>
+      <c r="H8" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="M8" s="20" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B9" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="20"/>
+      <c r="D9" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="20"/>
+      <c r="F9" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="7" t="s">
+      <c r="I9" s="20"/>
+      <c r="J9" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="7" t="s">
+      <c r="K9" s="20"/>
+      <c r="L9" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M9" s="20" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B10" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="25"/>
+      <c r="D10" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="23"/>
+      <c r="J10" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" s="25" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3043,7 +3087,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/영천 아리랑.xlsx
+++ b/sheets/민요/검수/영천 아리랑.xlsx
@@ -2766,17 +2766,17 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
   </cols>
   <sheetData>
